--- a/app/public/インボイス-パッキングリスト-取引先用.xlsx
+++ b/app/public/インボイス-パッキングリスト-取引先用.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\masuda-vinyl-ops\app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2292F546-58FB-4300-8B23-A6A622ECBC40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6BBCED-2C52-4FF4-BFDA-25C69E4E52C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="522" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1416" yWindow="-24168" windowWidth="32328" windowHeight="23016" tabRatio="522" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INVOICE" sheetId="1" r:id="rId1"/>
@@ -2933,6 +2933,255 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="14" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="14" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="14" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="14" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="14" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="186" fontId="14" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="14" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3168,255 +3417,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="14" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="14" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="14" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="184" fontId="14" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="2" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="14" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="186" fontId="14" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="2" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3445,6 +3445,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="INVOICE"/>
@@ -4216,62 +4217,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="13.5" customHeight="1">
-      <c r="A1" s="190" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="190"/>
-      <c r="C1" s="190"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="190"/>
-      <c r="F1" s="190"/>
-      <c r="G1" s="190"/>
-      <c r="H1" s="190"/>
-      <c r="I1" s="190"/>
-      <c r="J1" s="190"/>
-      <c r="K1" s="190"/>
-      <c r="L1" s="190"/>
+      <c r="A1" s="273" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="273"/>
+      <c r="C1" s="273"/>
+      <c r="D1" s="273"/>
+      <c r="E1" s="273"/>
+      <c r="F1" s="273"/>
+      <c r="G1" s="273"/>
+      <c r="H1" s="273"/>
+      <c r="I1" s="273"/>
+      <c r="J1" s="273"/>
+      <c r="K1" s="273"/>
+      <c r="L1" s="273"/>
     </row>
     <row r="2" spans="1:12" ht="7.5" customHeight="1">
-      <c r="A2" s="190"/>
-      <c r="B2" s="190"/>
-      <c r="C2" s="190"/>
-      <c r="D2" s="190"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
-      <c r="I2" s="190"/>
-      <c r="J2" s="190"/>
-      <c r="K2" s="190"/>
-      <c r="L2" s="190"/>
+      <c r="A2" s="273"/>
+      <c r="B2" s="273"/>
+      <c r="C2" s="273"/>
+      <c r="D2" s="273"/>
+      <c r="E2" s="273"/>
+      <c r="F2" s="273"/>
+      <c r="G2" s="273"/>
+      <c r="H2" s="273"/>
+      <c r="I2" s="273"/>
+      <c r="J2" s="273"/>
+      <c r="K2" s="273"/>
+      <c r="L2" s="273"/>
     </row>
     <row r="3" spans="1:12" ht="3.75" customHeight="1">
-      <c r="A3" s="190"/>
-      <c r="B3" s="190"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="190"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="190"/>
-      <c r="I3" s="190"/>
-      <c r="J3" s="190"/>
-      <c r="K3" s="190"/>
-      <c r="L3" s="190"/>
+      <c r="A3" s="273"/>
+      <c r="B3" s="273"/>
+      <c r="C3" s="273"/>
+      <c r="D3" s="273"/>
+      <c r="E3" s="273"/>
+      <c r="F3" s="273"/>
+      <c r="G3" s="273"/>
+      <c r="H3" s="273"/>
+      <c r="I3" s="273"/>
+      <c r="J3" s="273"/>
+      <c r="K3" s="273"/>
+      <c r="L3" s="273"/>
     </row>
     <row r="4" spans="1:12" ht="5.45" customHeight="1">
-      <c r="A4" s="190"/>
-      <c r="B4" s="190"/>
-      <c r="C4" s="190"/>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
-      <c r="I4" s="190"/>
-      <c r="J4" s="190"/>
-      <c r="K4" s="190"/>
-      <c r="L4" s="190"/>
+      <c r="A4" s="273"/>
+      <c r="B4" s="273"/>
+      <c r="C4" s="273"/>
+      <c r="D4" s="273"/>
+      <c r="E4" s="273"/>
+      <c r="F4" s="273"/>
+      <c r="G4" s="273"/>
+      <c r="H4" s="273"/>
+      <c r="I4" s="273"/>
+      <c r="J4" s="273"/>
+      <c r="K4" s="273"/>
+      <c r="L4" s="273"/>
     </row>
     <row r="5" spans="1:12">
       <c r="H5" s="41" t="s">
@@ -4289,20 +4290,20 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="26"/>
-      <c r="H7" s="200" t="s">
+      <c r="H7" s="283" t="s">
         <v>77</v>
       </c>
-      <c r="I7" s="201"/>
-      <c r="J7" s="201"/>
-      <c r="K7" s="202"/>
+      <c r="I7" s="284"/>
+      <c r="J7" s="284"/>
+      <c r="K7" s="285"/>
     </row>
     <row r="8" spans="1:12" ht="7.5" customHeight="1">
       <c r="A8" s="7"/>
       <c r="G8" s="27"/>
-      <c r="H8" s="203"/>
-      <c r="I8" s="204"/>
-      <c r="J8" s="204"/>
-      <c r="K8" s="205"/>
+      <c r="H8" s="286"/>
+      <c r="I8" s="287"/>
+      <c r="J8" s="287"/>
+      <c r="K8" s="288"/>
     </row>
     <row r="9" spans="1:12" ht="13.5" customHeight="1">
       <c r="A9" s="25" t="s">
@@ -4314,10 +4315,10 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="28"/>
-      <c r="H9" s="203"/>
-      <c r="I9" s="204"/>
-      <c r="J9" s="204"/>
-      <c r="K9" s="205"/>
+      <c r="H9" s="286"/>
+      <c r="I9" s="287"/>
+      <c r="J9" s="287"/>
+      <c r="K9" s="288"/>
     </row>
     <row r="10" spans="1:12" ht="13.5" customHeight="1">
       <c r="A10" s="23" t="s">
@@ -4329,14 +4330,14 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="24"/>
-      <c r="H10" s="206" t="s">
+      <c r="H10" s="289" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="207"/>
-      <c r="J10" s="210" t="s">
+      <c r="I10" s="290"/>
+      <c r="J10" s="293" t="s">
         <v>5</v>
       </c>
-      <c r="K10" s="211"/>
+      <c r="K10" s="294"/>
     </row>
     <row r="11" spans="1:12" ht="24" customHeight="1">
       <c r="A11" s="23" t="s">
@@ -4348,10 +4349,10 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="24"/>
-      <c r="H11" s="208"/>
-      <c r="I11" s="209"/>
-      <c r="J11" s="212"/>
-      <c r="K11" s="213"/>
+      <c r="H11" s="291"/>
+      <c r="I11" s="292"/>
+      <c r="J11" s="295"/>
+      <c r="K11" s="296"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="23" t="s">
@@ -4361,30 +4362,30 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="218"/>
-      <c r="G12" s="219"/>
-      <c r="H12" s="214" t="s">
+      <c r="F12" s="301"/>
+      <c r="G12" s="302"/>
+      <c r="H12" s="297" t="s">
         <v>7</v>
       </c>
-      <c r="I12" s="215"/>
-      <c r="J12" s="216" t="s">
+      <c r="I12" s="298"/>
+      <c r="J12" s="299" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="217"/>
+      <c r="K12" s="300"/>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="23" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="1"/>
-      <c r="F13" s="179"/>
-      <c r="G13" s="220"/>
-      <c r="H13" s="191" t="s">
+      <c r="F13" s="262"/>
+      <c r="G13" s="303"/>
+      <c r="H13" s="274" t="s">
         <v>10</v>
       </c>
-      <c r="I13" s="192"/>
-      <c r="J13" s="192"/>
-      <c r="K13" s="193"/>
+      <c r="I13" s="275"/>
+      <c r="J13" s="275"/>
+      <c r="K13" s="276"/>
     </row>
     <row r="14" spans="1:12" ht="3" customHeight="1">
       <c r="A14" s="8"/>
@@ -4394,10 +4395,10 @@
       <c r="E14" s="9"/>
       <c r="F14" s="29"/>
       <c r="G14" s="30"/>
-      <c r="H14" s="223"/>
-      <c r="I14" s="224"/>
-      <c r="J14" s="224"/>
-      <c r="K14" s="225"/>
+      <c r="H14" s="306"/>
+      <c r="I14" s="307"/>
+      <c r="J14" s="307"/>
+      <c r="K14" s="308"/>
     </row>
     <row r="15" spans="1:12" ht="18" customHeight="1">
       <c r="A15" s="10" t="s">
@@ -4409,26 +4410,26 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="31"/>
-      <c r="H15" s="196"/>
-      <c r="I15" s="226"/>
-      <c r="J15" s="226"/>
-      <c r="K15" s="227"/>
+      <c r="H15" s="279"/>
+      <c r="I15" s="309"/>
+      <c r="J15" s="309"/>
+      <c r="K15" s="310"/>
     </row>
     <row r="16" spans="1:12" ht="13.5" hidden="1" customHeight="1">
       <c r="A16" s="12"/>
       <c r="G16" s="27"/>
-      <c r="H16" s="196"/>
-      <c r="I16" s="226"/>
-      <c r="J16" s="226"/>
-      <c r="K16" s="227"/>
+      <c r="H16" s="279"/>
+      <c r="I16" s="309"/>
+      <c r="J16" s="309"/>
+      <c r="K16" s="310"/>
     </row>
     <row r="17" spans="1:11" ht="3.75" customHeight="1">
       <c r="A17" s="12"/>
       <c r="G17" s="27"/>
-      <c r="H17" s="196"/>
-      <c r="I17" s="226"/>
-      <c r="J17" s="226"/>
-      <c r="K17" s="227"/>
+      <c r="H17" s="279"/>
+      <c r="I17" s="309"/>
+      <c r="J17" s="309"/>
+      <c r="K17" s="310"/>
     </row>
     <row r="18" spans="1:11" ht="20.25">
       <c r="A18" s="34" t="s">
@@ -4439,10 +4440,10 @@
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="G18" s="27"/>
-      <c r="H18" s="198"/>
-      <c r="I18" s="228"/>
-      <c r="J18" s="228"/>
-      <c r="K18" s="229"/>
+      <c r="H18" s="281"/>
+      <c r="I18" s="311"/>
+      <c r="J18" s="311"/>
+      <c r="K18" s="312"/>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="40" t="s">
@@ -4476,8 +4477,8 @@
       <c r="C21" s="1"/>
       <c r="D21" s="45"/>
       <c r="E21" s="45"/>
-      <c r="F21" s="221"/>
-      <c r="G21" s="222"/>
+      <c r="F21" s="304"/>
+      <c r="G21" s="305"/>
       <c r="H21" s="113" t="s">
         <v>59</v>
       </c>
@@ -4494,8 +4495,8 @@
       <c r="C22" s="1"/>
       <c r="D22" s="45"/>
       <c r="E22" s="45"/>
-      <c r="F22" s="221"/>
-      <c r="G22" s="222"/>
+      <c r="F22" s="304"/>
+      <c r="G22" s="305"/>
       <c r="H22" s="115"/>
       <c r="I22" s="114" t="s">
         <v>61</v>
@@ -4505,23 +4506,23 @@
     <row r="23" spans="1:11">
       <c r="A23" s="16"/>
       <c r="B23" s="17"/>
-      <c r="C23" s="246"/>
-      <c r="D23" s="246"/>
-      <c r="E23" s="246"/>
-      <c r="F23" s="246"/>
+      <c r="C23" s="329"/>
+      <c r="D23" s="329"/>
+      <c r="E23" s="329"/>
+      <c r="F23" s="329"/>
       <c r="G23" s="30"/>
       <c r="K23" s="13"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="247" t="s">
+      <c r="A24" s="330" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="248"/>
-      <c r="C24" s="248"/>
-      <c r="D24" s="248"/>
-      <c r="E24" s="248"/>
-      <c r="F24" s="248"/>
-      <c r="G24" s="249"/>
+      <c r="B24" s="331"/>
+      <c r="C24" s="331"/>
+      <c r="D24" s="331"/>
+      <c r="E24" s="331"/>
+      <c r="F24" s="331"/>
+      <c r="G24" s="332"/>
       <c r="H24" s="115"/>
       <c r="I24" s="53" t="s">
         <v>62</v>
@@ -4529,15 +4530,15 @@
       <c r="K24" s="13"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="250" t="s">
+      <c r="A25" s="333" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="251"/>
-      <c r="C25" s="251"/>
-      <c r="D25" s="251"/>
-      <c r="E25" s="251"/>
-      <c r="F25" s="251"/>
-      <c r="G25" s="252"/>
+      <c r="B25" s="334"/>
+      <c r="C25" s="334"/>
+      <c r="D25" s="334"/>
+      <c r="E25" s="334"/>
+      <c r="F25" s="334"/>
+      <c r="G25" s="335"/>
       <c r="H25" s="115"/>
       <c r="I25" s="53" t="s">
         <v>63</v>
@@ -4545,15 +4546,15 @@
       <c r="K25" s="13"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="230" t="s">
+      <c r="A26" s="313" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="231"/>
-      <c r="C26" s="231"/>
-      <c r="D26" s="231"/>
-      <c r="E26" s="231"/>
-      <c r="F26" s="231"/>
-      <c r="G26" s="231"/>
+      <c r="B26" s="314"/>
+      <c r="C26" s="314"/>
+      <c r="D26" s="314"/>
+      <c r="E26" s="314"/>
+      <c r="F26" s="314"/>
+      <c r="G26" s="314"/>
       <c r="H26" s="115"/>
       <c r="I26" s="53" t="s">
         <v>64</v>
@@ -4561,15 +4562,15 @@
       <c r="K26" s="13"/>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" thickBot="1">
-      <c r="A27" s="232" t="s">
+      <c r="A27" s="315" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="233"/>
-      <c r="C27" s="233"/>
-      <c r="D27" s="233"/>
-      <c r="E27" s="233"/>
-      <c r="F27" s="233"/>
-      <c r="G27" s="234"/>
+      <c r="B27" s="316"/>
+      <c r="C27" s="316"/>
+      <c r="D27" s="316"/>
+      <c r="E27" s="316"/>
+      <c r="F27" s="316"/>
+      <c r="G27" s="317"/>
       <c r="H27" s="42"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -4579,79 +4580,79 @@
       <c r="H28" s="43"/>
     </row>
     <row r="29" spans="1:11" ht="6" customHeight="1">
-      <c r="A29" s="235" t="s">
+      <c r="A29" s="318" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="236"/>
-      <c r="C29" s="236"/>
-      <c r="D29" s="239" t="s">
+      <c r="B29" s="319"/>
+      <c r="C29" s="319"/>
+      <c r="D29" s="322" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="239" t="s">
+      <c r="E29" s="322" t="s">
         <v>19</v>
       </c>
-      <c r="F29" s="243" t="s">
+      <c r="F29" s="326" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="241" t="s">
+      <c r="G29" s="324" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="194" t="s">
+      <c r="H29" s="277" t="s">
         <v>54</v>
       </c>
-      <c r="I29" s="195"/>
-      <c r="J29" s="253" t="s">
+      <c r="I29" s="278"/>
+      <c r="J29" s="336" t="s">
         <v>55</v>
       </c>
-      <c r="K29" s="254"/>
+      <c r="K29" s="337"/>
     </row>
     <row r="30" spans="1:11" ht="9.75" customHeight="1">
-      <c r="A30" s="237"/>
-      <c r="B30" s="238"/>
-      <c r="C30" s="238"/>
-      <c r="D30" s="240"/>
-      <c r="E30" s="240"/>
-      <c r="F30" s="244"/>
-      <c r="G30" s="238"/>
-      <c r="H30" s="196"/>
-      <c r="I30" s="197"/>
-      <c r="J30" s="238"/>
-      <c r="K30" s="255"/>
+      <c r="A30" s="320"/>
+      <c r="B30" s="321"/>
+      <c r="C30" s="321"/>
+      <c r="D30" s="323"/>
+      <c r="E30" s="323"/>
+      <c r="F30" s="327"/>
+      <c r="G30" s="321"/>
+      <c r="H30" s="279"/>
+      <c r="I30" s="280"/>
+      <c r="J30" s="321"/>
+      <c r="K30" s="338"/>
     </row>
     <row r="31" spans="1:11" ht="9.75" customHeight="1">
-      <c r="A31" s="237"/>
-      <c r="B31" s="238"/>
-      <c r="C31" s="238"/>
-      <c r="D31" s="240"/>
-      <c r="E31" s="240"/>
-      <c r="F31" s="244"/>
-      <c r="G31" s="238"/>
-      <c r="H31" s="196"/>
-      <c r="I31" s="197"/>
-      <c r="J31" s="238"/>
-      <c r="K31" s="255"/>
+      <c r="A31" s="320"/>
+      <c r="B31" s="321"/>
+      <c r="C31" s="321"/>
+      <c r="D31" s="323"/>
+      <c r="E31" s="323"/>
+      <c r="F31" s="327"/>
+      <c r="G31" s="321"/>
+      <c r="H31" s="279"/>
+      <c r="I31" s="280"/>
+      <c r="J31" s="321"/>
+      <c r="K31" s="338"/>
     </row>
     <row r="32" spans="1:11" ht="21" customHeight="1">
-      <c r="A32" s="237"/>
-      <c r="B32" s="238"/>
-      <c r="C32" s="238"/>
-      <c r="D32" s="257"/>
-      <c r="E32" s="240"/>
-      <c r="F32" s="245"/>
-      <c r="G32" s="242"/>
-      <c r="H32" s="198"/>
-      <c r="I32" s="199"/>
-      <c r="J32" s="242"/>
-      <c r="K32" s="256"/>
+      <c r="A32" s="320"/>
+      <c r="B32" s="321"/>
+      <c r="C32" s="321"/>
+      <c r="D32" s="340"/>
+      <c r="E32" s="323"/>
+      <c r="F32" s="328"/>
+      <c r="G32" s="325"/>
+      <c r="H32" s="281"/>
+      <c r="I32" s="282"/>
+      <c r="J32" s="325"/>
+      <c r="K32" s="339"/>
     </row>
     <row r="33" spans="1:11" ht="27.2" customHeight="1">
       <c r="A33" s="47">
         <v>1</v>
       </c>
-      <c r="B33" s="186" t="s">
+      <c r="B33" s="269" t="s">
         <v>48</v>
       </c>
-      <c r="C33" s="187"/>
+      <c r="C33" s="270"/>
       <c r="D33" s="50" t="e">
         <f>VLOOKUP(B33,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -4666,26 +4667,26 @@
       <c r="G33" s="52">
         <v>300</v>
       </c>
-      <c r="H33" s="188" t="e">
+      <c r="H33" s="271" t="e">
         <f>VLOOKUP(B33,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I33" s="188"/>
-      <c r="J33" s="188" t="e">
+      <c r="I33" s="271"/>
+      <c r="J33" s="271" t="e">
         <f t="shared" ref="J33" si="0">H33*G33</f>
         <v>#REF!</v>
       </c>
-      <c r="K33" s="189"/>
+      <c r="K33" s="272"/>
     </row>
     <row r="34" spans="1:11" ht="27.2" customHeight="1">
       <c r="A34" s="47">
         <f>A33+1</f>
         <v>2</v>
       </c>
-      <c r="B34" s="186" t="s">
+      <c r="B34" s="269" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="187"/>
+      <c r="C34" s="270"/>
       <c r="D34" s="50" t="e">
         <f>VLOOKUP(B34,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -4700,26 +4701,26 @@
       <c r="G34" s="52">
         <v>300</v>
       </c>
-      <c r="H34" s="188" t="e">
+      <c r="H34" s="271" t="e">
         <f>VLOOKUP(B34,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I34" s="188"/>
-      <c r="J34" s="188" t="e">
+      <c r="I34" s="271"/>
+      <c r="J34" s="271" t="e">
         <f t="shared" ref="J34:J40" si="1">H34*G34</f>
         <v>#REF!</v>
       </c>
-      <c r="K34" s="189"/>
+      <c r="K34" s="272"/>
     </row>
     <row r="35" spans="1:11" ht="25.5" customHeight="1">
       <c r="A35" s="47">
         <f t="shared" ref="A35:A50" si="2">A34+1</f>
         <v>3</v>
       </c>
-      <c r="B35" s="186" t="s">
+      <c r="B35" s="269" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="187"/>
+      <c r="C35" s="270"/>
       <c r="D35" s="50" t="e">
         <f>VLOOKUP(B35,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -4734,26 +4735,26 @@
       <c r="G35" s="52">
         <v>329</v>
       </c>
-      <c r="H35" s="188" t="e">
+      <c r="H35" s="271" t="e">
         <f>VLOOKUP(B35,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I35" s="188"/>
-      <c r="J35" s="188" t="e">
+      <c r="I35" s="271"/>
+      <c r="J35" s="271" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="K35" s="189"/>
+      <c r="K35" s="272"/>
     </row>
     <row r="36" spans="1:11" ht="28.5" customHeight="1">
       <c r="A36" s="47">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="B36" s="186" t="s">
+      <c r="B36" s="269" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="187"/>
+      <c r="C36" s="270"/>
       <c r="D36" s="50" t="e">
         <f>VLOOKUP(B36,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -4768,26 +4769,26 @@
       <c r="G36" s="52">
         <v>331</v>
       </c>
-      <c r="H36" s="188" t="e">
+      <c r="H36" s="271" t="e">
         <f>VLOOKUP(B36,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I36" s="188"/>
-      <c r="J36" s="188" t="e">
+      <c r="I36" s="271"/>
+      <c r="J36" s="271" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="K36" s="189"/>
+      <c r="K36" s="272"/>
     </row>
     <row r="37" spans="1:11" ht="32.25" customHeight="1">
       <c r="A37" s="47">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="B37" s="186" t="s">
+      <c r="B37" s="269" t="s">
         <v>56</v>
       </c>
-      <c r="C37" s="187"/>
+      <c r="C37" s="270"/>
       <c r="D37" s="50" t="e">
         <f>VLOOKUP(B37,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -4802,26 +4803,26 @@
       <c r="G37" s="52">
         <v>640</v>
       </c>
-      <c r="H37" s="188" t="e">
+      <c r="H37" s="271" t="e">
         <f>VLOOKUP(B37,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I37" s="188"/>
-      <c r="J37" s="188" t="e">
+      <c r="I37" s="271"/>
+      <c r="J37" s="271" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="K37" s="189"/>
+      <c r="K37" s="272"/>
     </row>
     <row r="38" spans="1:11" ht="32.25" customHeight="1">
       <c r="A38" s="47">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="B38" s="186" t="s">
+      <c r="B38" s="269" t="s">
         <v>43</v>
       </c>
-      <c r="C38" s="187"/>
+      <c r="C38" s="270"/>
       <c r="D38" s="50" t="e">
         <f>VLOOKUP(B38,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -4836,26 +4837,26 @@
       <c r="G38" s="52">
         <v>300</v>
       </c>
-      <c r="H38" s="188" t="e">
+      <c r="H38" s="271" t="e">
         <f>VLOOKUP(B38,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I38" s="188"/>
-      <c r="J38" s="188" t="e">
+      <c r="I38" s="271"/>
+      <c r="J38" s="271" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="K38" s="189"/>
+      <c r="K38" s="272"/>
     </row>
     <row r="39" spans="1:11" ht="26.25" customHeight="1">
       <c r="A39" s="47">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="B39" s="186" t="s">
+      <c r="B39" s="269" t="s">
         <v>44</v>
       </c>
-      <c r="C39" s="187"/>
+      <c r="C39" s="270"/>
       <c r="D39" s="50" t="e">
         <f>VLOOKUP(B39,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -4870,26 +4871,26 @@
       <c r="G39" s="52">
         <v>300</v>
       </c>
-      <c r="H39" s="188" t="e">
+      <c r="H39" s="271" t="e">
         <f>VLOOKUP(B39,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I39" s="188"/>
-      <c r="J39" s="188" t="e">
+      <c r="I39" s="271"/>
+      <c r="J39" s="271" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="K39" s="189"/>
+      <c r="K39" s="272"/>
     </row>
     <row r="40" spans="1:11" ht="26.25" customHeight="1">
       <c r="A40" s="47">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="B40" s="186" t="s">
+      <c r="B40" s="269" t="s">
         <v>42</v>
       </c>
-      <c r="C40" s="187"/>
+      <c r="C40" s="270"/>
       <c r="D40" s="50" t="e">
         <f>VLOOKUP(B40,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -4904,26 +4905,26 @@
       <c r="G40" s="52">
         <v>300</v>
       </c>
-      <c r="H40" s="188" t="e">
+      <c r="H40" s="271" t="e">
         <f>VLOOKUP(B40,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I40" s="188"/>
-      <c r="J40" s="188" t="e">
+      <c r="I40" s="271"/>
+      <c r="J40" s="271" t="e">
         <f t="shared" si="1"/>
         <v>#REF!</v>
       </c>
-      <c r="K40" s="189"/>
+      <c r="K40" s="272"/>
     </row>
     <row r="41" spans="1:11" ht="26.25" customHeight="1">
       <c r="A41" s="47">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="B41" s="186" t="s">
+      <c r="B41" s="269" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="187"/>
+      <c r="C41" s="270"/>
       <c r="D41" s="50" t="e">
         <f>VLOOKUP(B41,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -4938,26 +4939,26 @@
       <c r="G41" s="52">
         <v>300</v>
       </c>
-      <c r="H41" s="188" t="e">
+      <c r="H41" s="271" t="e">
         <f>VLOOKUP(B41,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I41" s="188"/>
-      <c r="J41" s="188" t="e">
+      <c r="I41" s="271"/>
+      <c r="J41" s="271" t="e">
         <f t="shared" ref="J41:J43" si="3">H41*G41</f>
         <v>#REF!</v>
       </c>
-      <c r="K41" s="189"/>
+      <c r="K41" s="272"/>
     </row>
     <row r="42" spans="1:11" ht="26.25" customHeight="1">
       <c r="A42" s="47">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="B42" s="186" t="s">
+      <c r="B42" s="269" t="s">
         <v>23</v>
       </c>
-      <c r="C42" s="187"/>
+      <c r="C42" s="270"/>
       <c r="D42" s="50" t="e">
         <f>VLOOKUP(B42,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -4972,26 +4973,26 @@
       <c r="G42" s="52">
         <v>300</v>
       </c>
-      <c r="H42" s="188" t="e">
+      <c r="H42" s="271" t="e">
         <f>VLOOKUP(B42,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I42" s="188"/>
-      <c r="J42" s="188" t="e">
+      <c r="I42" s="271"/>
+      <c r="J42" s="271" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
-      <c r="K42" s="189"/>
+      <c r="K42" s="272"/>
     </row>
     <row r="43" spans="1:11" ht="26.25" customHeight="1">
       <c r="A43" s="47">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="B43" s="186" t="s">
+      <c r="B43" s="269" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="187"/>
+      <c r="C43" s="270"/>
       <c r="D43" s="50" t="e">
         <f>VLOOKUP(B43,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -5006,26 +5007,26 @@
       <c r="G43" s="52">
         <v>300</v>
       </c>
-      <c r="H43" s="188" t="e">
+      <c r="H43" s="271" t="e">
         <f>VLOOKUP(B43,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I43" s="188"/>
-      <c r="J43" s="188" t="e">
+      <c r="I43" s="271"/>
+      <c r="J43" s="271" t="e">
         <f t="shared" si="3"/>
         <v>#REF!</v>
       </c>
-      <c r="K43" s="189"/>
+      <c r="K43" s="272"/>
     </row>
     <row r="44" spans="1:11" ht="31.5" customHeight="1">
       <c r="A44" s="47">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="B44" s="186" t="s">
+      <c r="B44" s="269" t="s">
         <v>51</v>
       </c>
-      <c r="C44" s="187"/>
+      <c r="C44" s="270"/>
       <c r="D44" s="50" t="e">
         <f>VLOOKUP(B44,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -5040,26 +5041,26 @@
       <c r="G44" s="52">
         <v>323</v>
       </c>
-      <c r="H44" s="188" t="e">
+      <c r="H44" s="271" t="e">
         <f>VLOOKUP(B44,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I44" s="188"/>
-      <c r="J44" s="188" t="e">
+      <c r="I44" s="271"/>
+      <c r="J44" s="271" t="e">
         <f t="shared" ref="J44:J45" si="4">H44*G44</f>
         <v>#REF!</v>
       </c>
-      <c r="K44" s="189"/>
+      <c r="K44" s="272"/>
     </row>
     <row r="45" spans="1:11" ht="26.25" customHeight="1">
       <c r="A45" s="47">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="B45" s="186" t="s">
+      <c r="B45" s="269" t="s">
         <v>52</v>
       </c>
-      <c r="C45" s="187"/>
+      <c r="C45" s="270"/>
       <c r="D45" s="50" t="e">
         <f>VLOOKUP(B45,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -5074,26 +5075,26 @@
       <c r="G45" s="52">
         <v>6</v>
       </c>
-      <c r="H45" s="188" t="e">
+      <c r="H45" s="271" t="e">
         <f>VLOOKUP(B45,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I45" s="188"/>
-      <c r="J45" s="188" t="e">
+      <c r="I45" s="271"/>
+      <c r="J45" s="271" t="e">
         <f t="shared" si="4"/>
         <v>#REF!</v>
       </c>
-      <c r="K45" s="189"/>
+      <c r="K45" s="272"/>
     </row>
     <row r="46" spans="1:11" ht="26.25" customHeight="1">
       <c r="A46" s="47">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="B46" s="186" t="s">
+      <c r="B46" s="269" t="s">
         <v>67</v>
       </c>
-      <c r="C46" s="187"/>
+      <c r="C46" s="270"/>
       <c r="D46" s="50" t="e">
         <f>VLOOKUP(B46,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -5108,26 +5109,26 @@
       <c r="G46" s="52">
         <v>13</v>
       </c>
-      <c r="H46" s="188" t="e">
+      <c r="H46" s="271" t="e">
         <f>VLOOKUP(B46,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I46" s="188"/>
-      <c r="J46" s="188" t="e">
+      <c r="I46" s="271"/>
+      <c r="J46" s="271" t="e">
         <f t="shared" ref="J46" si="5">H46*G46</f>
         <v>#REF!</v>
       </c>
-      <c r="K46" s="189"/>
+      <c r="K46" s="272"/>
     </row>
     <row r="47" spans="1:11" ht="26.25" customHeight="1">
       <c r="A47" s="47">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="B47" s="186" t="s">
+      <c r="B47" s="269" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="187"/>
+      <c r="C47" s="270"/>
       <c r="D47" s="50" t="e">
         <f>VLOOKUP(B47,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -5142,26 +5143,26 @@
       <c r="G47" s="52">
         <v>300</v>
       </c>
-      <c r="H47" s="188" t="e">
+      <c r="H47" s="271" t="e">
         <f>VLOOKUP(B47,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I47" s="188"/>
-      <c r="J47" s="188" t="e">
+      <c r="I47" s="271"/>
+      <c r="J47" s="271" t="e">
         <f t="shared" ref="J47" si="6">H47*G47</f>
         <v>#REF!</v>
       </c>
-      <c r="K47" s="189"/>
+      <c r="K47" s="272"/>
     </row>
     <row r="48" spans="1:11" ht="30.75" customHeight="1">
       <c r="A48" s="47">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="B48" s="186" t="s">
+      <c r="B48" s="269" t="s">
         <v>50</v>
       </c>
-      <c r="C48" s="187"/>
+      <c r="C48" s="270"/>
       <c r="D48" s="50" t="e">
         <f>VLOOKUP(B48,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -5176,26 +5177,26 @@
       <c r="G48" s="52">
         <v>320</v>
       </c>
-      <c r="H48" s="188" t="e">
+      <c r="H48" s="271" t="e">
         <f>VLOOKUP(B48,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I48" s="188"/>
-      <c r="J48" s="188" t="e">
+      <c r="I48" s="271"/>
+      <c r="J48" s="271" t="e">
         <f t="shared" ref="J48:J49" si="7">H48*G48</f>
         <v>#REF!</v>
       </c>
-      <c r="K48" s="189"/>
+      <c r="K48" s="272"/>
     </row>
     <row r="49" spans="1:11" ht="30.75" customHeight="1">
       <c r="A49" s="47">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="B49" s="186" t="s">
+      <c r="B49" s="269" t="s">
         <v>53</v>
       </c>
-      <c r="C49" s="187"/>
+      <c r="C49" s="270"/>
       <c r="D49" s="50" t="e">
         <f>VLOOKUP(B49,#REF!,2,FALSE)</f>
         <v>#REF!</v>
@@ -5210,65 +5211,65 @@
       <c r="G49" s="52">
         <v>80</v>
       </c>
-      <c r="H49" s="188" t="e">
+      <c r="H49" s="271" t="e">
         <f>VLOOKUP(B49,#REF!,3,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="I49" s="188"/>
-      <c r="J49" s="188" t="e">
+      <c r="I49" s="271"/>
+      <c r="J49" s="271" t="e">
         <f t="shared" si="7"/>
         <v>#REF!</v>
       </c>
-      <c r="K49" s="189"/>
+      <c r="K49" s="272"/>
     </row>
     <row r="50" spans="1:11" ht="30.75" customHeight="1">
       <c r="A50" s="47">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="B50" s="186"/>
-      <c r="C50" s="187"/>
+      <c r="B50" s="269"/>
+      <c r="C50" s="270"/>
       <c r="D50" s="50"/>
       <c r="E50" s="56"/>
       <c r="F50" s="51"/>
       <c r="G50" s="52"/>
-      <c r="H50" s="188"/>
-      <c r="I50" s="188"/>
-      <c r="J50" s="188"/>
-      <c r="K50" s="189"/>
+      <c r="H50" s="271"/>
+      <c r="I50" s="271"/>
+      <c r="J50" s="271"/>
+      <c r="K50" s="272"/>
     </row>
     <row r="51" spans="1:11" ht="24.75" customHeight="1" thickBot="1">
-      <c r="A51" s="183" t="s">
+      <c r="A51" s="266" t="s">
         <v>25</v>
       </c>
-      <c r="B51" s="184"/>
-      <c r="C51" s="184"/>
-      <c r="D51" s="184"/>
-      <c r="E51" s="184"/>
-      <c r="F51" s="184"/>
-      <c r="G51" s="184"/>
-      <c r="H51" s="184"/>
-      <c r="I51" s="185"/>
-      <c r="J51" s="180" t="e">
+      <c r="B51" s="267"/>
+      <c r="C51" s="267"/>
+      <c r="D51" s="267"/>
+      <c r="E51" s="267"/>
+      <c r="F51" s="267"/>
+      <c r="G51" s="267"/>
+      <c r="H51" s="267"/>
+      <c r="I51" s="268"/>
+      <c r="J51" s="263" t="e">
         <f>SUM(J33:K50)</f>
         <v>#REF!</v>
       </c>
-      <c r="K51" s="181"/>
+      <c r="K51" s="264"/>
     </row>
     <row r="52" spans="1:11" ht="13.5" customHeight="1"/>
     <row r="53" spans="1:11" ht="24.75" customHeight="1">
-      <c r="A53" s="182" t="s">
+      <c r="A53" s="265" t="s">
         <v>26</v>
       </c>
-      <c r="B53" s="182"/>
-      <c r="C53" s="182"/>
-      <c r="D53" s="182"/>
-      <c r="E53" s="182"/>
-      <c r="H53" s="179" t="s">
+      <c r="B53" s="265"/>
+      <c r="C53" s="265"/>
+      <c r="D53" s="265"/>
+      <c r="E53" s="265"/>
+      <c r="H53" s="262" t="s">
         <v>27</v>
       </c>
-      <c r="I53" s="179"/>
-      <c r="J53" s="179"/>
+      <c r="I53" s="262"/>
+      <c r="J53" s="262"/>
       <c r="K53" s="33"/>
     </row>
     <row r="54" spans="1:11" ht="20.100000000000001" customHeight="1">
@@ -5435,76 +5436,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="272" t="s">
+      <c r="A1" s="193" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="272"/>
-      <c r="C1" s="272"/>
-      <c r="D1" s="272"/>
-      <c r="E1" s="272"/>
-      <c r="F1" s="272"/>
-      <c r="G1" s="272"/>
-      <c r="H1" s="272"/>
-      <c r="I1" s="272"/>
-      <c r="J1" s="272"/>
-      <c r="K1" s="272"/>
-      <c r="L1" s="272"/>
-      <c r="M1" s="272"/>
+      <c r="B1" s="193"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="193"/>
+      <c r="J1" s="193"/>
+      <c r="K1" s="193"/>
+      <c r="L1" s="193"/>
+      <c r="M1" s="193"/>
     </row>
     <row r="2" spans="1:14" ht="9.1999999999999993" customHeight="1">
-      <c r="A2" s="272"/>
-      <c r="B2" s="272"/>
-      <c r="C2" s="272"/>
-      <c r="D2" s="272"/>
-      <c r="E2" s="272"/>
-      <c r="F2" s="272"/>
-      <c r="G2" s="272"/>
-      <c r="H2" s="272"/>
-      <c r="I2" s="272"/>
-      <c r="J2" s="272"/>
-      <c r="K2" s="272"/>
-      <c r="L2" s="272"/>
-      <c r="M2" s="272"/>
+      <c r="A2" s="193"/>
+      <c r="B2" s="193"/>
+      <c r="C2" s="193"/>
+      <c r="D2" s="193"/>
+      <c r="E2" s="193"/>
+      <c r="F2" s="193"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="193"/>
+      <c r="J2" s="193"/>
+      <c r="K2" s="193"/>
+      <c r="L2" s="193"/>
+      <c r="M2" s="193"/>
     </row>
     <row r="3" spans="1:14" ht="3" customHeight="1">
-      <c r="A3" s="272"/>
-      <c r="B3" s="272"/>
-      <c r="C3" s="272"/>
-      <c r="D3" s="272"/>
-      <c r="E3" s="272"/>
-      <c r="F3" s="272"/>
-      <c r="G3" s="272"/>
-      <c r="H3" s="272"/>
-      <c r="I3" s="272"/>
-      <c r="J3" s="272"/>
-      <c r="K3" s="272"/>
-      <c r="L3" s="272"/>
-      <c r="M3" s="272"/>
+      <c r="A3" s="193"/>
+      <c r="B3" s="193"/>
+      <c r="C3" s="193"/>
+      <c r="D3" s="193"/>
+      <c r="E3" s="193"/>
+      <c r="F3" s="193"/>
+      <c r="G3" s="193"/>
+      <c r="H3" s="193"/>
+      <c r="I3" s="193"/>
+      <c r="J3" s="193"/>
+      <c r="K3" s="193"/>
+      <c r="L3" s="193"/>
+      <c r="M3" s="193"/>
     </row>
     <row r="4" spans="1:14" ht="4.5" customHeight="1">
-      <c r="A4" s="272"/>
-      <c r="B4" s="272"/>
-      <c r="C4" s="272"/>
-      <c r="D4" s="272"/>
-      <c r="E4" s="272"/>
-      <c r="F4" s="272"/>
-      <c r="G4" s="272"/>
-      <c r="H4" s="272"/>
-      <c r="I4" s="272"/>
-      <c r="J4" s="272"/>
-      <c r="K4" s="272"/>
-      <c r="L4" s="272"/>
-      <c r="M4" s="272"/>
+      <c r="A4" s="193"/>
+      <c r="B4" s="193"/>
+      <c r="C4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="193"/>
+      <c r="K4" s="193"/>
+      <c r="L4" s="193"/>
+      <c r="M4" s="193"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="I5" s="298" t="str">
+      <c r="I5" s="219" t="str">
         <f>INVOICE!H5</f>
         <v>インボイス作成日（Date): 24/11/2025</v>
       </c>
-      <c r="J5" s="298"/>
-      <c r="K5" s="298"/>
-      <c r="L5" s="298"/>
-      <c r="M5" s="298"/>
+      <c r="J5" s="219"/>
+      <c r="K5" s="219"/>
+      <c r="L5" s="219"/>
+      <c r="M5" s="219"/>
     </row>
     <row r="7" spans="1:14" ht="9.75" customHeight="1" thickBot="1"/>
     <row r="8" spans="1:14" ht="14.25" customHeight="1">
@@ -5518,24 +5519,24 @@
       <c r="F8" s="58"/>
       <c r="G8" s="58"/>
       <c r="H8" s="59"/>
-      <c r="I8" s="276" t="str">
+      <c r="I8" s="197" t="str">
         <f>INVOICE!H7</f>
         <v>Invoice No
 [Invoice No]</v>
       </c>
-      <c r="J8" s="277"/>
-      <c r="K8" s="277"/>
-      <c r="L8" s="277"/>
-      <c r="M8" s="277"/>
+      <c r="J8" s="198"/>
+      <c r="K8" s="198"/>
+      <c r="L8" s="198"/>
+      <c r="M8" s="198"/>
     </row>
     <row r="9" spans="1:14" ht="6.75" customHeight="1">
       <c r="A9" s="61"/>
       <c r="H9" s="62"/>
-      <c r="I9" s="278"/>
-      <c r="J9" s="279"/>
-      <c r="K9" s="279"/>
-      <c r="L9" s="279"/>
-      <c r="M9" s="279"/>
+      <c r="I9" s="199"/>
+      <c r="J9" s="200"/>
+      <c r="K9" s="200"/>
+      <c r="L9" s="200"/>
+      <c r="M9" s="200"/>
     </row>
     <row r="10" spans="1:14" ht="12.75" customHeight="1">
       <c r="A10" s="63" t="s">
@@ -5548,11 +5549,11 @@
       <c r="F10" s="64"/>
       <c r="G10" s="65"/>
       <c r="H10" s="62"/>
-      <c r="I10" s="278"/>
-      <c r="J10" s="279"/>
-      <c r="K10" s="279"/>
-      <c r="L10" s="279"/>
-      <c r="M10" s="279"/>
+      <c r="I10" s="199"/>
+      <c r="J10" s="200"/>
+      <c r="K10" s="200"/>
+      <c r="L10" s="200"/>
+      <c r="M10" s="200"/>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1">
       <c r="A11" s="66" t="s">
@@ -5565,15 +5566,15 @@
       <c r="F11" s="64"/>
       <c r="G11" s="68"/>
       <c r="H11" s="62"/>
-      <c r="I11" s="299" t="s">
+      <c r="I11" s="220" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="300"/>
-      <c r="K11" s="301"/>
-      <c r="L11" s="299" t="s">
+      <c r="J11" s="221"/>
+      <c r="K11" s="222"/>
+      <c r="L11" s="220" t="s">
         <v>5</v>
       </c>
-      <c r="M11" s="300"/>
+      <c r="M11" s="221"/>
       <c r="N11" s="121"/>
     </row>
     <row r="12" spans="1:14">
@@ -5587,11 +5588,11 @@
       <c r="F12" s="64"/>
       <c r="G12" s="68"/>
       <c r="H12" s="62"/>
-      <c r="I12" s="302"/>
-      <c r="J12" s="303"/>
-      <c r="K12" s="304"/>
-      <c r="L12" s="302"/>
-      <c r="M12" s="303"/>
+      <c r="I12" s="223"/>
+      <c r="J12" s="224"/>
+      <c r="K12" s="225"/>
+      <c r="L12" s="223"/>
+      <c r="M12" s="224"/>
       <c r="N12" s="121"/>
     </row>
     <row r="13" spans="1:14">
@@ -5605,16 +5606,16 @@
       <c r="F13" s="69"/>
       <c r="G13" s="70"/>
       <c r="H13" s="62"/>
-      <c r="I13" s="307" t="s">
+      <c r="I13" s="228" t="s">
         <v>7</v>
       </c>
-      <c r="J13" s="308"/>
-      <c r="K13" s="309"/>
-      <c r="L13" s="307" t="str">
+      <c r="J13" s="229"/>
+      <c r="K13" s="230"/>
+      <c r="L13" s="228" t="str">
         <f>INVOICE!J12</f>
         <v>INDONESIA</v>
       </c>
-      <c r="M13" s="308"/>
+      <c r="M13" s="229"/>
       <c r="N13" s="122"/>
     </row>
     <row r="14" spans="1:14">
@@ -5625,13 +5626,13 @@
       <c r="F14" s="71"/>
       <c r="G14" s="72"/>
       <c r="H14" s="62"/>
-      <c r="I14" s="280" t="s">
+      <c r="I14" s="201" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="280"/>
-      <c r="K14" s="280"/>
-      <c r="L14" s="281"/>
-      <c r="M14" s="281"/>
+      <c r="J14" s="201"/>
+      <c r="K14" s="201"/>
+      <c r="L14" s="202"/>
+      <c r="M14" s="202"/>
     </row>
     <row r="15" spans="1:14" ht="6" customHeight="1">
       <c r="A15" s="66"/>
@@ -5639,14 +5640,14 @@
       <c r="F15" s="72"/>
       <c r="G15" s="72"/>
       <c r="H15" s="62"/>
-      <c r="I15" s="284">
-        <f>INVOICE!H14</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="285"/>
-      <c r="K15" s="285"/>
-      <c r="L15" s="285"/>
-      <c r="M15" s="285"/>
+      <c r="I15" s="205" t="str">
+        <f>IF(NOT(INVOICE!H14=""), INVOICE!H14, "")</f>
+        <v/>
+      </c>
+      <c r="J15" s="206"/>
+      <c r="K15" s="206"/>
+      <c r="L15" s="206"/>
+      <c r="M15" s="206"/>
     </row>
     <row r="16" spans="1:14" ht="9.1999999999999993" customHeight="1">
       <c r="A16" s="73"/>
@@ -5657,11 +5658,11 @@
       <c r="F16" s="74"/>
       <c r="G16" s="74"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="284"/>
-      <c r="J16" s="285"/>
-      <c r="K16" s="285"/>
-      <c r="L16" s="285"/>
-      <c r="M16" s="285"/>
+      <c r="I16" s="205"/>
+      <c r="J16" s="206"/>
+      <c r="K16" s="206"/>
+      <c r="L16" s="206"/>
+      <c r="M16" s="206"/>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="76" t="s">
@@ -5674,11 +5675,11 @@
       <c r="F17" s="77"/>
       <c r="G17" s="77"/>
       <c r="H17" s="62"/>
-      <c r="I17" s="286"/>
-      <c r="J17" s="287"/>
-      <c r="K17" s="287"/>
-      <c r="L17" s="287"/>
-      <c r="M17" s="287"/>
+      <c r="I17" s="207"/>
+      <c r="J17" s="208"/>
+      <c r="K17" s="208"/>
+      <c r="L17" s="208"/>
+      <c r="M17" s="208"/>
     </row>
     <row r="18" spans="1:21" ht="15" hidden="1" customHeight="1">
       <c r="A18" s="78"/>
@@ -5740,13 +5741,13 @@
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="A23" s="322" t="str">
+      <c r="A23" s="243" t="str">
         <f>INVOICE!A21</f>
         <v>TEL :62-21-8975220 ext : 252</v>
       </c>
-      <c r="B23" s="323"/>
-      <c r="C23" s="323"/>
-      <c r="D23" s="323"/>
+      <c r="B23" s="244"/>
+      <c r="C23" s="244"/>
+      <c r="D23" s="244"/>
       <c r="E23" s="82"/>
       <c r="F23" s="69"/>
       <c r="G23" s="69"/>
@@ -5756,9 +5757,12 @@
       <c r="M23" s="60"/>
     </row>
     <row r="24" spans="1:21" ht="14.25" customHeight="1">
-      <c r="A24" s="282"/>
-      <c r="B24" s="283"/>
-      <c r="C24" s="283"/>
+      <c r="A24" s="203" t="str">
+        <f>INVOICE!A22</f>
+        <v>TAX ID: 001.558.251.3-056.000</v>
+      </c>
+      <c r="B24" s="204"/>
+      <c r="C24" s="204"/>
       <c r="D24" s="67"/>
       <c r="E24" s="67"/>
       <c r="F24" s="69"/>
@@ -5773,10 +5777,10 @@
     <row r="25" spans="1:21" ht="12.75" customHeight="1">
       <c r="A25" s="83"/>
       <c r="B25" s="84"/>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="261"/>
+      <c r="D25" s="261"/>
+      <c r="E25" s="261"/>
+      <c r="F25" s="261"/>
       <c r="G25" s="74"/>
       <c r="H25" s="75"/>
       <c r="I25" s="113"/>
@@ -5786,16 +5790,16 @@
       <c r="M25" s="60"/>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="328" t="s">
+      <c r="A26" s="249" t="s">
         <v>14</v>
       </c>
-      <c r="B26" s="329"/>
-      <c r="C26" s="329"/>
-      <c r="D26" s="329"/>
-      <c r="E26" s="329"/>
-      <c r="F26" s="329"/>
-      <c r="G26" s="329"/>
-      <c r="H26" s="329"/>
+      <c r="B26" s="250"/>
+      <c r="C26" s="250"/>
+      <c r="D26" s="250"/>
+      <c r="E26" s="250"/>
+      <c r="F26" s="250"/>
+      <c r="G26" s="250"/>
+      <c r="H26" s="250"/>
       <c r="I26" s="113"/>
       <c r="J26" s="53" t="s">
         <v>64</v>
@@ -5803,45 +5807,45 @@
       <c r="M26" s="60"/>
     </row>
     <row r="27" spans="1:21" ht="15" customHeight="1">
-      <c r="A27" s="330" t="s">
+      <c r="A27" s="251" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="331"/>
-      <c r="C27" s="331"/>
-      <c r="D27" s="331"/>
-      <c r="E27" s="331"/>
-      <c r="F27" s="331"/>
-      <c r="G27" s="331"/>
-      <c r="H27" s="331"/>
+      <c r="B27" s="252"/>
+      <c r="C27" s="252"/>
+      <c r="D27" s="252"/>
+      <c r="E27" s="252"/>
+      <c r="F27" s="252"/>
+      <c r="G27" s="252"/>
+      <c r="H27" s="252"/>
       <c r="I27" s="116"/>
       <c r="M27" s="60"/>
     </row>
     <row r="28" spans="1:21">
-      <c r="A28" s="332" t="s">
+      <c r="A28" s="253" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="333"/>
-      <c r="C28" s="333"/>
-      <c r="D28" s="333"/>
-      <c r="E28" s="333"/>
-      <c r="F28" s="333"/>
-      <c r="G28" s="333"/>
-      <c r="H28" s="334"/>
+      <c r="B28" s="254"/>
+      <c r="C28" s="254"/>
+      <c r="D28" s="254"/>
+      <c r="E28" s="254"/>
+      <c r="F28" s="254"/>
+      <c r="G28" s="254"/>
+      <c r="H28" s="255"/>
       <c r="I28" s="85"/>
       <c r="M28" s="60"/>
     </row>
     <row r="29" spans="1:21" ht="15.75" thickBot="1">
-      <c r="A29" s="324" t="str">
+      <c r="A29" s="245" t="str">
         <f>INVOICE!A27</f>
         <v>JAKARTA INDONESIA</v>
       </c>
-      <c r="B29" s="325"/>
-      <c r="C29" s="325"/>
-      <c r="D29" s="325"/>
-      <c r="E29" s="325"/>
-      <c r="F29" s="325"/>
-      <c r="G29" s="325"/>
-      <c r="H29" s="326"/>
+      <c r="B29" s="246"/>
+      <c r="C29" s="246"/>
+      <c r="D29" s="246"/>
+      <c r="E29" s="246"/>
+      <c r="F29" s="246"/>
+      <c r="G29" s="246"/>
+      <c r="H29" s="247"/>
       <c r="I29" s="86"/>
       <c r="J29" s="87"/>
       <c r="K29" s="87"/>
@@ -5858,59 +5862,59 @@
       <c r="G30" s="35"/>
     </row>
     <row r="31" spans="1:21" ht="14.1" customHeight="1">
-      <c r="A31" s="290" t="str">
+      <c r="A31" s="211" t="str">
         <f>INVOICE!A29</f>
         <v>品番
 ( Part No)</v>
       </c>
-      <c r="B31" s="291"/>
-      <c r="C31" s="291"/>
-      <c r="D31" s="295" t="str">
+      <c r="B31" s="212"/>
+      <c r="C31" s="212"/>
+      <c r="D31" s="216" t="str">
         <f>INVOICE!D29</f>
         <v>品名
 (Part Name)</v>
       </c>
-      <c r="E31" s="295" t="s">
+      <c r="E31" s="216" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="273" t="s">
+      <c r="F31" s="194" t="s">
         <v>31</v>
       </c>
-      <c r="G31" s="327" t="s">
+      <c r="G31" s="248" t="s">
         <v>21</v>
       </c>
-      <c r="H31" s="311" t="s">
+      <c r="H31" s="232" t="s">
         <v>32</v>
       </c>
-      <c r="I31" s="335"/>
-      <c r="J31" s="295" t="s">
+      <c r="I31" s="256"/>
+      <c r="J31" s="216" t="s">
         <v>33</v>
       </c>
-      <c r="K31" s="311" t="s">
+      <c r="K31" s="232" t="s">
         <v>34</v>
       </c>
-      <c r="L31" s="305" t="s">
+      <c r="L31" s="226" t="s">
         <v>35</v>
       </c>
-      <c r="M31" s="288" t="s">
+      <c r="M31" s="209" t="s">
         <v>36</v>
       </c>
       <c r="R31" s="117"/>
     </row>
     <row r="32" spans="1:21" ht="9.75" customHeight="1">
-      <c r="A32" s="292"/>
-      <c r="B32" s="258"/>
-      <c r="C32" s="258"/>
-      <c r="D32" s="296"/>
-      <c r="E32" s="338"/>
-      <c r="F32" s="274"/>
-      <c r="G32" s="258"/>
-      <c r="H32" s="336"/>
-      <c r="I32" s="337"/>
-      <c r="J32" s="296"/>
-      <c r="K32" s="312"/>
-      <c r="L32" s="306"/>
-      <c r="M32" s="289"/>
+      <c r="A32" s="213"/>
+      <c r="B32" s="179"/>
+      <c r="C32" s="179"/>
+      <c r="D32" s="217"/>
+      <c r="E32" s="259"/>
+      <c r="F32" s="195"/>
+      <c r="G32" s="179"/>
+      <c r="H32" s="257"/>
+      <c r="I32" s="258"/>
+      <c r="J32" s="217"/>
+      <c r="K32" s="233"/>
+      <c r="L32" s="227"/>
+      <c r="M32" s="210"/>
       <c r="N32" s="18"/>
       <c r="O32" s="18"/>
       <c r="P32" s="18"/>
@@ -5921,19 +5925,19 @@
       <c r="U32" s="18"/>
     </row>
     <row r="33" spans="1:21" ht="11.25" customHeight="1">
-      <c r="A33" s="292"/>
-      <c r="B33" s="258"/>
-      <c r="C33" s="258"/>
-      <c r="D33" s="296"/>
-      <c r="E33" s="338"/>
-      <c r="F33" s="274"/>
-      <c r="G33" s="258"/>
-      <c r="H33" s="336"/>
-      <c r="I33" s="337"/>
-      <c r="J33" s="296"/>
-      <c r="K33" s="312"/>
-      <c r="L33" s="306"/>
-      <c r="M33" s="289"/>
+      <c r="A33" s="213"/>
+      <c r="B33" s="179"/>
+      <c r="C33" s="179"/>
+      <c r="D33" s="217"/>
+      <c r="E33" s="259"/>
+      <c r="F33" s="195"/>
+      <c r="G33" s="179"/>
+      <c r="H33" s="257"/>
+      <c r="I33" s="258"/>
+      <c r="J33" s="217"/>
+      <c r="K33" s="233"/>
+      <c r="L33" s="227"/>
+      <c r="M33" s="210"/>
       <c r="N33" s="18"/>
       <c r="O33" s="19"/>
       <c r="P33" s="19"/>
@@ -5944,19 +5948,19 @@
       <c r="U33" s="21"/>
     </row>
     <row r="34" spans="1:21">
-      <c r="A34" s="293"/>
-      <c r="B34" s="294"/>
-      <c r="C34" s="294"/>
-      <c r="D34" s="297"/>
-      <c r="E34" s="339"/>
-      <c r="F34" s="275"/>
-      <c r="G34" s="294"/>
-      <c r="H34" s="336"/>
-      <c r="I34" s="337"/>
-      <c r="J34" s="297"/>
-      <c r="K34" s="313"/>
-      <c r="L34" s="306"/>
-      <c r="M34" s="289"/>
+      <c r="A34" s="214"/>
+      <c r="B34" s="215"/>
+      <c r="C34" s="215"/>
+      <c r="D34" s="218"/>
+      <c r="E34" s="260"/>
+      <c r="F34" s="196"/>
+      <c r="G34" s="215"/>
+      <c r="H34" s="257"/>
+      <c r="I34" s="258"/>
+      <c r="J34" s="218"/>
+      <c r="K34" s="234"/>
+      <c r="L34" s="227"/>
+      <c r="M34" s="210"/>
       <c r="N34" s="18"/>
       <c r="O34" s="19"/>
       <c r="P34" s="19"/>
@@ -5970,11 +5974,11 @@
       <c r="A35" s="91">
         <v>1</v>
       </c>
-      <c r="B35" s="258" t="str">
+      <c r="B35" s="179" t="str">
         <f>INVOICE!B33</f>
         <v>LDBA043800-2</v>
       </c>
-      <c r="C35" s="258"/>
+      <c r="C35" s="179"/>
       <c r="D35" s="92" t="e">
         <f>INVOICE!D33</f>
         <v>#REF!</v>
@@ -5991,11 +5995,11 @@
         <f>INVOICE!G33</f>
         <v>300</v>
       </c>
-      <c r="H35" s="306">
+      <c r="H35" s="227">
         <f>_xlfn.XLOOKUP(B35,データ!B:B,データ!F:F,"")</f>
         <v>40</v>
       </c>
-      <c r="I35" s="274"/>
+      <c r="I35" s="195"/>
       <c r="J35" s="52">
         <f>IFERROR(ROUNDUP(G35/H35,0),"")</f>
         <v>8</v>
@@ -6023,11 +6027,11 @@
         <f t="shared" ref="A36" si="0">A35+1</f>
         <v>2</v>
       </c>
-      <c r="B36" s="258" t="str">
+      <c r="B36" s="179" t="str">
         <f>INVOICE!B34</f>
         <v>LDBA043900-2</v>
       </c>
-      <c r="C36" s="258"/>
+      <c r="C36" s="179"/>
       <c r="D36" s="92" t="e">
         <f>INVOICE!D34</f>
         <v>#REF!</v>
@@ -6044,11 +6048,11 @@
         <f>INVOICE!G34</f>
         <v>300</v>
       </c>
-      <c r="H36" s="306">
+      <c r="H36" s="227">
         <f>_xlfn.XLOOKUP(B36,データ!B:B,データ!F:F,"")</f>
         <v>46</v>
       </c>
-      <c r="I36" s="274"/>
+      <c r="I36" s="195"/>
       <c r="J36" s="52">
         <f t="shared" ref="J36:J51" si="1">IFERROR(ROUNDUP(G36/H36,0),"")</f>
         <v>7</v>
@@ -6076,11 +6080,11 @@
         <f>A36+1</f>
         <v>3</v>
       </c>
-      <c r="B37" s="258" t="str">
+      <c r="B37" s="179" t="str">
         <f>INVOICE!B35</f>
         <v>LDBA044901-2</v>
       </c>
-      <c r="C37" s="258"/>
+      <c r="C37" s="179"/>
       <c r="D37" s="92" t="e">
         <f>INVOICE!D35</f>
         <v>#REF!</v>
@@ -6097,11 +6101,11 @@
         <f>INVOICE!G35</f>
         <v>329</v>
       </c>
-      <c r="H37" s="306">
+      <c r="H37" s="227">
         <f>_xlfn.XLOOKUP(B37,データ!B:B,データ!F:F,"")</f>
         <v>42</v>
       </c>
-      <c r="I37" s="274"/>
+      <c r="I37" s="195"/>
       <c r="J37" s="52">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -6129,11 +6133,11 @@
         <f>A37+1</f>
         <v>4</v>
       </c>
-      <c r="B38" s="258" t="str">
+      <c r="B38" s="179" t="str">
         <f>INVOICE!B36</f>
         <v>LDBA045001-2</v>
       </c>
-      <c r="C38" s="258"/>
+      <c r="C38" s="179"/>
       <c r="D38" s="92" t="e">
         <f>INVOICE!D36</f>
         <v>#REF!</v>
@@ -6150,11 +6154,11 @@
         <f>INVOICE!G36</f>
         <v>331</v>
       </c>
-      <c r="H38" s="306">
+      <c r="H38" s="227">
         <f>_xlfn.XLOOKUP(B38,データ!B:B,データ!F:F,"")</f>
         <v>42</v>
       </c>
-      <c r="I38" s="274"/>
+      <c r="I38" s="195"/>
       <c r="J38" s="52">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -6182,11 +6186,11 @@
         <f t="shared" ref="A39:A52" si="4">A38+1</f>
         <v>5</v>
       </c>
-      <c r="B39" s="258" t="str">
+      <c r="B39" s="179" t="str">
         <f>INVOICE!B37</f>
         <v>LDBA045101-3</v>
       </c>
-      <c r="C39" s="258"/>
+      <c r="C39" s="179"/>
       <c r="D39" s="92" t="e">
         <f>INVOICE!D37</f>
         <v>#REF!</v>
@@ -6204,11 +6208,11 @@
         <f>INVOICE!G37</f>
         <v>640</v>
       </c>
-      <c r="H39" s="306">
+      <c r="H39" s="227">
         <f>_xlfn.XLOOKUP(B39,データ!B:B,データ!F:F,"")</f>
         <v>40</v>
       </c>
-      <c r="I39" s="274"/>
+      <c r="I39" s="195"/>
       <c r="J39" s="52">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -6236,11 +6240,11 @@
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="B40" s="258" t="str">
+      <c r="B40" s="179" t="str">
         <f>INVOICE!B38</f>
         <v>LDBA053601-2</v>
       </c>
-      <c r="C40" s="258"/>
+      <c r="C40" s="179"/>
       <c r="D40" s="92" t="e">
         <f>INVOICE!D38</f>
         <v>#REF!</v>
@@ -6257,11 +6261,11 @@
         <f>INVOICE!G38</f>
         <v>300</v>
       </c>
-      <c r="H40" s="306">
+      <c r="H40" s="227">
         <f>_xlfn.XLOOKUP(B40,データ!B:B,データ!F:F,"")</f>
         <v>80</v>
       </c>
-      <c r="I40" s="274"/>
+      <c r="I40" s="195"/>
       <c r="J40" s="52">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -6289,11 +6293,11 @@
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="B41" s="258" t="str">
+      <c r="B41" s="179" t="str">
         <f>INVOICE!B39</f>
         <v>LDBA064301-2</v>
       </c>
-      <c r="C41" s="258"/>
+      <c r="C41" s="179"/>
       <c r="D41" s="92" t="e">
         <f>INVOICE!D39</f>
         <v>#REF!</v>
@@ -6310,11 +6314,11 @@
         <f>INVOICE!G39</f>
         <v>300</v>
       </c>
-      <c r="H41" s="306">
+      <c r="H41" s="227">
         <f>_xlfn.XLOOKUP(B41,データ!B:B,データ!F:F,"")</f>
         <v>80</v>
       </c>
-      <c r="I41" s="274"/>
+      <c r="I41" s="195"/>
       <c r="J41" s="52">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -6342,11 +6346,11 @@
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="B42" s="258" t="str">
+      <c r="B42" s="179" t="str">
         <f>INVOICE!B40</f>
         <v>LDBA053603-0</v>
       </c>
-      <c r="C42" s="258"/>
+      <c r="C42" s="179"/>
       <c r="D42" s="92" t="e">
         <f>INVOICE!D40</f>
         <v>#REF!</v>
@@ -6363,11 +6367,11 @@
         <f>INVOICE!G40</f>
         <v>300</v>
       </c>
-      <c r="H42" s="306">
+      <c r="H42" s="227">
         <f>_xlfn.XLOOKUP(B42,データ!B:B,データ!F:F,"")</f>
         <v>80</v>
       </c>
-      <c r="I42" s="274"/>
+      <c r="I42" s="195"/>
       <c r="J42" s="52">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -6395,11 +6399,11 @@
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="B43" s="258" t="str">
+      <c r="B43" s="179" t="str">
         <f>INVOICE!B41</f>
         <v>LDBA064303-0</v>
       </c>
-      <c r="C43" s="258"/>
+      <c r="C43" s="179"/>
       <c r="D43" s="92" t="e">
         <f>INVOICE!D41</f>
         <v>#REF!</v>
@@ -6416,11 +6420,11 @@
         <f>INVOICE!G41</f>
         <v>300</v>
       </c>
-      <c r="H43" s="306">
+      <c r="H43" s="227">
         <f>_xlfn.XLOOKUP(B43,データ!B:B,データ!F:F,"")</f>
         <v>80</v>
       </c>
-      <c r="I43" s="274"/>
+      <c r="I43" s="195"/>
       <c r="J43" s="52">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -6448,11 +6452,11 @@
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="B44" s="258" t="str">
+      <c r="B44" s="179" t="str">
         <f>INVOICE!B42</f>
         <v>LDBA053700-0</v>
       </c>
-      <c r="C44" s="258"/>
+      <c r="C44" s="179"/>
       <c r="D44" s="92" t="e">
         <f>INVOICE!D42</f>
         <v>#REF!</v>
@@ -6469,11 +6473,11 @@
         <f>INVOICE!G42</f>
         <v>300</v>
       </c>
-      <c r="H44" s="306">
+      <c r="H44" s="227">
         <f>_xlfn.XLOOKUP(B44,データ!B:B,データ!F:F,"")</f>
         <v>50</v>
       </c>
-      <c r="I44" s="274"/>
+      <c r="I44" s="195"/>
       <c r="J44" s="52">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -6501,11 +6505,11 @@
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="B45" s="258" t="str">
+      <c r="B45" s="179" t="str">
         <f>INVOICE!B43</f>
         <v>LDBA053800-0</v>
       </c>
-      <c r="C45" s="258"/>
+      <c r="C45" s="179"/>
       <c r="D45" s="92" t="e">
         <f>INVOICE!D43</f>
         <v>#REF!</v>
@@ -6522,11 +6526,11 @@
         <f>INVOICE!G43</f>
         <v>300</v>
       </c>
-      <c r="H45" s="306">
+      <c r="H45" s="227">
         <f>_xlfn.XLOOKUP(B45,データ!B:B,データ!F:F,"")</f>
         <v>50</v>
       </c>
-      <c r="I45" s="274"/>
+      <c r="I45" s="195"/>
       <c r="J45" s="52">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -6554,11 +6558,11 @@
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="B46" s="258" t="str">
+      <c r="B46" s="179" t="str">
         <f>INVOICE!B44</f>
         <v>LDBA061200-0</v>
       </c>
-      <c r="C46" s="258"/>
+      <c r="C46" s="179"/>
       <c r="D46" s="92" t="e">
         <f>INVOICE!D44</f>
         <v>#REF!</v>
@@ -6576,11 +6580,11 @@
         <f>INVOICE!G44</f>
         <v>323</v>
       </c>
-      <c r="H46" s="306">
+      <c r="H46" s="227">
         <f>_xlfn.XLOOKUP(B46,データ!B:B,データ!F:F,"")</f>
         <v>20</v>
       </c>
-      <c r="I46" s="274"/>
+      <c r="I46" s="195"/>
       <c r="J46" s="52">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -6608,11 +6612,11 @@
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="B47" s="258" t="str">
+      <c r="B47" s="179" t="str">
         <f>INVOICE!B45</f>
         <v>LDBA061300-0</v>
       </c>
-      <c r="C47" s="258"/>
+      <c r="C47" s="179"/>
       <c r="D47" s="92" t="e">
         <f>INVOICE!D45</f>
         <v>#REF!</v>
@@ -6629,11 +6633,11 @@
         <f>INVOICE!G45</f>
         <v>6</v>
       </c>
-      <c r="H47" s="306">
+      <c r="H47" s="227">
         <f>_xlfn.XLOOKUP(B47,データ!B:B,データ!F:F,"")</f>
         <v>20</v>
       </c>
-      <c r="I47" s="274"/>
+      <c r="I47" s="195"/>
       <c r="J47" s="52">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -6661,11 +6665,11 @@
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="B48" s="258" t="str">
+      <c r="B48" s="179" t="str">
         <f>INVOICE!B46</f>
         <v>LDBA093301-0</v>
       </c>
-      <c r="C48" s="258"/>
+      <c r="C48" s="179"/>
       <c r="D48" s="92" t="e">
         <f>INVOICE!D46</f>
         <v>#REF!</v>
@@ -6682,11 +6686,11 @@
         <f>INVOICE!G46</f>
         <v>13</v>
       </c>
-      <c r="H48" s="306">
+      <c r="H48" s="227">
         <f>_xlfn.XLOOKUP(B48,データ!B:B,データ!F:F,"")</f>
         <v>80</v>
       </c>
-      <c r="I48" s="274"/>
+      <c r="I48" s="195"/>
       <c r="J48" s="52">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -6714,11 +6718,11 @@
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="B49" s="258" t="str">
+      <c r="B49" s="179" t="str">
         <f>INVOICE!B47</f>
         <v>LDBA053500-0</v>
       </c>
-      <c r="C49" s="258"/>
+      <c r="C49" s="179"/>
       <c r="D49" s="92" t="e">
         <f>INVOICE!D47</f>
         <v>#REF!</v>
@@ -6735,11 +6739,11 @@
         <f>INVOICE!G47</f>
         <v>300</v>
       </c>
-      <c r="H49" s="306">
+      <c r="H49" s="227">
         <f>_xlfn.XLOOKUP(B49,データ!B:B,データ!F:F,"")</f>
         <v>170</v>
       </c>
-      <c r="I49" s="274"/>
+      <c r="I49" s="195"/>
       <c r="J49" s="52">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -6767,11 +6771,11 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="B50" s="258" t="str">
+      <c r="B50" s="179" t="str">
         <f>INVOICE!B48</f>
         <v>LDBA060800-0</v>
       </c>
-      <c r="C50" s="258"/>
+      <c r="C50" s="179"/>
       <c r="D50" s="92" t="e">
         <f>INVOICE!D48</f>
         <v>#REF!</v>
@@ -6788,11 +6792,11 @@
         <f>INVOICE!G48</f>
         <v>320</v>
       </c>
-      <c r="H50" s="306">
+      <c r="H50" s="227">
         <f>_xlfn.XLOOKUP(B50,データ!B:B,データ!F:F,"")</f>
         <v>34</v>
       </c>
-      <c r="I50" s="274"/>
+      <c r="I50" s="195"/>
       <c r="J50" s="52">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -6820,11 +6824,11 @@
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="B51" s="258" t="str">
+      <c r="B51" s="179" t="str">
         <f>INVOICE!B49</f>
         <v>LDBA060501-1</v>
       </c>
-      <c r="C51" s="258"/>
+      <c r="C51" s="179"/>
       <c r="D51" s="92" t="e">
         <f>INVOICE!D49</f>
         <v>#REF!</v>
@@ -6841,11 +6845,11 @@
         <f>INVOICE!G49</f>
         <v>80</v>
       </c>
-      <c r="H51" s="306">
+      <c r="H51" s="227">
         <f>_xlfn.XLOOKUP(B51,データ!B:B,データ!F:F,"")</f>
         <v>22</v>
       </c>
-      <c r="I51" s="274"/>
+      <c r="I51" s="195"/>
       <c r="J51" s="52">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -6873,8 +6877,8 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="B52" s="258"/>
-      <c r="C52" s="258"/>
+      <c r="B52" s="179"/>
+      <c r="C52" s="179"/>
       <c r="D52" s="92"/>
       <c r="E52" s="56"/>
       <c r="F52" s="44"/>
@@ -6895,57 +6899,57 @@
       <c r="U52" s="21"/>
     </row>
     <row r="53" spans="1:21">
-      <c r="A53" s="260" t="s">
+      <c r="A53" s="181" t="s">
         <v>25</v>
       </c>
-      <c r="B53" s="261"/>
-      <c r="C53" s="261"/>
-      <c r="D53" s="261"/>
-      <c r="E53" s="261"/>
-      <c r="F53" s="262"/>
-      <c r="G53" s="314">
+      <c r="B53" s="182"/>
+      <c r="C53" s="182"/>
+      <c r="D53" s="182"/>
+      <c r="E53" s="182"/>
+      <c r="F53" s="183"/>
+      <c r="G53" s="235">
         <f>SUM(G35:G52)</f>
         <v>4742</v>
       </c>
-      <c r="H53" s="270"/>
-      <c r="I53" s="262"/>
-      <c r="J53" s="268">
+      <c r="H53" s="191"/>
+      <c r="I53" s="183"/>
+      <c r="J53" s="189">
         <f>SUM(J35:J52)</f>
         <v>110</v>
       </c>
-      <c r="K53" s="318">
+      <c r="K53" s="239">
         <f>SUM(K35:K52)</f>
         <v>0</v>
       </c>
-      <c r="L53" s="320">
+      <c r="L53" s="241">
         <f>SUM(L35:L52)</f>
         <v>0</v>
       </c>
-      <c r="M53" s="316">
+      <c r="M53" s="237">
         <f>SUM(M35:M52)</f>
         <v>254.70000000000002</v>
       </c>
-      <c r="N53" s="310"/>
-      <c r="O53" s="310"/>
-      <c r="P53" s="310"/>
+      <c r="N53" s="231"/>
+      <c r="O53" s="231"/>
+      <c r="P53" s="231"/>
     </row>
     <row r="54" spans="1:21" ht="13.5" customHeight="1" thickBot="1">
-      <c r="A54" s="263"/>
-      <c r="B54" s="264"/>
-      <c r="C54" s="264"/>
-      <c r="D54" s="264"/>
-      <c r="E54" s="264"/>
-      <c r="F54" s="265"/>
-      <c r="G54" s="315"/>
-      <c r="H54" s="271"/>
-      <c r="I54" s="265"/>
-      <c r="J54" s="269"/>
-      <c r="K54" s="319"/>
-      <c r="L54" s="321"/>
-      <c r="M54" s="317"/>
-      <c r="N54" s="310"/>
-      <c r="O54" s="310"/>
-      <c r="P54" s="310"/>
+      <c r="A54" s="184"/>
+      <c r="B54" s="185"/>
+      <c r="C54" s="185"/>
+      <c r="D54" s="185"/>
+      <c r="E54" s="185"/>
+      <c r="F54" s="186"/>
+      <c r="G54" s="236"/>
+      <c r="H54" s="192"/>
+      <c r="I54" s="186"/>
+      <c r="J54" s="190"/>
+      <c r="K54" s="240"/>
+      <c r="L54" s="242"/>
+      <c r="M54" s="238"/>
+      <c r="N54" s="231"/>
+      <c r="O54" s="231"/>
+      <c r="P54" s="231"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
       <c r="A55" s="94" t="str">
@@ -6957,11 +6961,11 @@
       <c r="T55" s="119"/>
     </row>
     <row r="56" spans="1:21" ht="18" customHeight="1">
-      <c r="A56" s="266" t="s">
+      <c r="A56" s="187" t="s">
         <v>45</v>
       </c>
-      <c r="B56" s="267"/>
-      <c r="C56" s="267"/>
+      <c r="B56" s="188"/>
+      <c r="C56" s="188"/>
       <c r="D56" s="95">
         <f>G53</f>
         <v>4742</v>
@@ -6969,9 +6973,9 @@
       <c r="E56" s="95"/>
       <c r="F56" s="96"/>
       <c r="G56" s="97"/>
-      <c r="H56" s="267"/>
-      <c r="I56" s="267"/>
-      <c r="J56" s="267"/>
+      <c r="H56" s="188"/>
+      <c r="I56" s="188"/>
+      <c r="J56" s="188"/>
       <c r="N56" s="120"/>
       <c r="O56" s="67"/>
     </row>
@@ -6987,11 +6991,11 @@
       <c r="F57" s="98"/>
       <c r="G57" s="99"/>
       <c r="H57" s="100"/>
-      <c r="I57" s="267" t="s">
+      <c r="I57" s="188" t="s">
         <v>27</v>
       </c>
-      <c r="J57" s="267"/>
-      <c r="K57" s="267"/>
+      <c r="J57" s="188"/>
+      <c r="K57" s="188"/>
       <c r="L57" s="35"/>
       <c r="N57" s="35"/>
       <c r="O57" s="67"/>
@@ -7013,9 +7017,9 @@
       </c>
     </row>
     <row r="60" spans="1:21" ht="15" customHeight="1">
-      <c r="A60" s="259"/>
-      <c r="B60" s="259"/>
-      <c r="C60" s="259"/>
+      <c r="A60" s="180"/>
+      <c r="B60" s="180"/>
+      <c r="C60" s="180"/>
       <c r="D60" s="104"/>
       <c r="E60" s="104"/>
     </row>
